--- a/final_data_pipeline/output/325211longform_elec_options_nowhp.xlsx
+++ b/final_data_pipeline/output/325211longform_elec_options_nowhp.xlsx
@@ -833,7 +833,7 @@
         <v>106</v>
       </c>
       <c r="I3">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="J3">
         <v>8000</v>
@@ -848,10 +848,10 @@
         <v>5238929.691068697</v>
       </c>
       <c r="N3">
-        <v>1.741590909090909</v>
+        <v>1.911855479578636</v>
       </c>
       <c r="O3">
-        <v>1.89075</v>
+        <v>2.09608909874769</v>
       </c>
       <c r="P3">
         <v>654.8662113835871</v>
@@ -1351,7 +1351,7 @@
         <v>107</v>
       </c>
       <c r="I13">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J13">
         <v>8000</v>
@@ -1398,7 +1398,7 @@
         <v>106</v>
       </c>
       <c r="I14">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J14">
         <v>8000</v>
@@ -1413,10 +1413,10 @@
         <v>615283.5854615972</v>
       </c>
       <c r="N14">
-        <v>1.741590909090909</v>
+        <v>1.940636870984383</v>
       </c>
       <c r="O14">
-        <v>1.89075</v>
+        <v>2.131200751448103</v>
       </c>
       <c r="P14">
         <v>76.91044818269965</v>
@@ -1557,7 +1557,7 @@
         <v>106</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="J17">
         <v>8000</v>
@@ -1572,10 +1572,10 @@
         <v>520144.2167393085</v>
       </c>
       <c r="N17">
-        <v>1.741590909090909</v>
+        <v>1.902494195535734</v>
       </c>
       <c r="O17">
-        <v>1.89075</v>
+        <v>2.084694111942012</v>
       </c>
       <c r="P17">
         <v>65.01802709241356</v>
@@ -1610,7 +1610,7 @@
         <v>106</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="J18">
         <v>8000</v>
@@ -1625,10 +1625,10 @@
         <v>305739.6316466416</v>
       </c>
       <c r="N18">
-        <v>1.741590909090909</v>
+        <v>1.837513876759573</v>
       </c>
       <c r="O18">
-        <v>1.89075</v>
+        <v>2.005936573945218</v>
       </c>
       <c r="P18">
         <v>38.2174539558302</v>
@@ -1769,7 +1769,7 @@
         <v>106</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>20.22222222222222</v>
       </c>
       <c r="J21">
         <v>8000</v>
@@ -1784,10 +1784,10 @@
         <v>2811791.13048226</v>
       </c>
       <c r="N21">
-        <v>1.741590909090909</v>
+        <v>1.920016703786191</v>
       </c>
       <c r="O21">
-        <v>1.89075</v>
+        <v>2.106033415841584</v>
       </c>
       <c r="P21">
         <v>351.4738913102825</v>
@@ -1822,7 +1822,7 @@
         <v>106</v>
       </c>
       <c r="I22">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="J22">
         <v>8000</v>
@@ -1837,10 +1837,10 @@
         <v>601898.1634017075</v>
       </c>
       <c r="N22">
-        <v>1.741590909090909</v>
+        <v>1.803186500133452</v>
       </c>
       <c r="O22">
-        <v>1.89075</v>
+        <v>1.964569140204562</v>
       </c>
       <c r="P22">
         <v>75.23727042521344</v>
@@ -1975,7 +1975,7 @@
         <v>106</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="J25">
         <v>8000</v>
@@ -1990,10 +1990,10 @@
         <v>345837.0124918807</v>
       </c>
       <c r="N25">
-        <v>1.741590909090909</v>
+        <v>1.789400236291612</v>
       </c>
       <c r="O25">
-        <v>1.89075</v>
+        <v>1.948001533154466</v>
       </c>
       <c r="P25">
         <v>43.22962656148508</v>
@@ -2028,7 +2028,7 @@
         <v>108</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="J26">
         <v>8000</v>
@@ -2281,7 +2281,7 @@
         <v>106</v>
       </c>
       <c r="I31">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="J31">
         <v>8000</v>
@@ -2296,10 +2296,10 @@
         <v>850414.8584661442</v>
       </c>
       <c r="N31">
-        <v>1.741590909090909</v>
+        <v>1.672941176470588</v>
       </c>
       <c r="O31">
-        <v>1.89075</v>
+        <v>1.809089700996678</v>
       </c>
       <c r="P31">
         <v>106.301857308268</v>
@@ -2334,7 +2334,7 @@
         <v>106</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J32">
         <v>8000</v>
@@ -2349,10 +2349,10 @@
         <v>276974.460834612</v>
       </c>
       <c r="N32">
-        <v>1.741590909090909</v>
+        <v>1.940636870984383</v>
       </c>
       <c r="O32">
-        <v>1.89075</v>
+        <v>2.131200751448103</v>
       </c>
       <c r="P32">
         <v>34.62180760432651</v>
@@ -2546,7 +2546,7 @@
         <v>106</v>
       </c>
       <c r="I36">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="J36">
         <v>8000</v>
@@ -2561,10 +2561,10 @@
         <v>333173.0506735449</v>
       </c>
       <c r="N36">
-        <v>1.741590909090909</v>
+        <v>1.620655622136059</v>
       </c>
       <c r="O36">
-        <v>1.89075</v>
+        <v>1.747323835194455</v>
       </c>
       <c r="P36">
         <v>41.64663133419311</v>
@@ -2599,7 +2599,7 @@
         <v>106</v>
       </c>
       <c r="I37">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="J37">
         <v>8000</v>
@@ -2614,10 +2614,10 @@
         <v>847644.9933633942</v>
       </c>
       <c r="N37">
-        <v>1.741590909090909</v>
+        <v>1.672941176470588</v>
       </c>
       <c r="O37">
-        <v>1.89075</v>
+        <v>1.809089700996678</v>
       </c>
       <c r="P37">
         <v>105.9556241704243</v>
@@ -2811,7 +2811,7 @@
         <v>106</v>
       </c>
       <c r="I41">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="J41">
         <v>8000</v>
@@ -2826,10 +2826,10 @@
         <v>526489.1191663315</v>
       </c>
       <c r="N41">
-        <v>1.741590909090909</v>
+        <v>1.902494195535734</v>
       </c>
       <c r="O41">
-        <v>1.89075</v>
+        <v>2.084694111942012</v>
       </c>
       <c r="P41">
         <v>65.81113989579144</v>
@@ -2917,7 +2917,7 @@
         <v>106</v>
       </c>
       <c r="I43">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="J43">
         <v>8000</v>
@@ -2932,10 +2932,10 @@
         <v>549800.0296599994</v>
       </c>
       <c r="N43">
-        <v>1.741590909090909</v>
+        <v>1.784922174701128</v>
       </c>
       <c r="O43">
-        <v>1.89075</v>
+        <v>1.942625691911729</v>
       </c>
       <c r="P43">
         <v>68.72500370749992</v>
@@ -3223,7 +3223,7 @@
         <v>106</v>
       </c>
       <c r="I49">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J49">
         <v>8000</v>
@@ -3238,10 +3238,10 @@
         <v>289694.1513146128</v>
       </c>
       <c r="N49">
-        <v>1.741590909090909</v>
+        <v>1.940636870984383</v>
       </c>
       <c r="O49">
-        <v>1.89075</v>
+        <v>2.131200751448103</v>
       </c>
       <c r="P49">
         <v>36.2117689143266</v>
@@ -3382,7 +3382,7 @@
         <v>106</v>
       </c>
       <c r="I52">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="J52">
         <v>8000</v>
@@ -3397,10 +3397,10 @@
         <v>979239.9438947932</v>
       </c>
       <c r="N52">
-        <v>1.741590909090909</v>
+        <v>1.80090088129692</v>
       </c>
       <c r="O52">
-        <v>1.89075</v>
+        <v>1.961820583643568</v>
       </c>
       <c r="P52">
         <v>122.4049929868492</v>
@@ -3541,7 +3541,7 @@
         <v>106</v>
       </c>
       <c r="I55">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="J55">
         <v>8000</v>
@@ -3556,10 +3556,10 @@
         <v>504275.1037852188</v>
       </c>
       <c r="N55">
-        <v>1.741590909090909</v>
+        <v>1.784922174701128</v>
       </c>
       <c r="O55">
-        <v>1.89075</v>
+        <v>1.942625691911729</v>
       </c>
       <c r="P55">
         <v>63.03438797315236</v>
@@ -3647,7 +3647,7 @@
         <v>106</v>
       </c>
       <c r="I57">
-        <v>10</v>
+        <v>12.67039049919483</v>
       </c>
       <c r="J57">
         <v>8000</v>
@@ -3662,10 +3662,10 @@
         <v>673940.0276347516</v>
       </c>
       <c r="N57">
-        <v>1.741590909090909</v>
+        <v>1.784922174701128</v>
       </c>
       <c r="O57">
-        <v>1.89075</v>
+        <v>1.942625691911729</v>
       </c>
       <c r="P57">
         <v>84.24250345434396</v>
@@ -3806,7 +3806,7 @@
         <v>106</v>
       </c>
       <c r="I60">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="J60">
         <v>8000</v>
@@ -3821,10 +3821,10 @@
         <v>535129.202006985</v>
       </c>
       <c r="N60">
-        <v>1.741590909090909</v>
+        <v>1.909121107266436</v>
       </c>
       <c r="O60">
-        <v>1.89075</v>
+        <v>2.092759415833974</v>
       </c>
       <c r="P60">
         <v>66.89115025087312</v>
@@ -4218,7 +4218,7 @@
         <v>106</v>
       </c>
       <c r="I68">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="J68">
         <v>8000</v>
@@ -4233,10 +4233,10 @@
         <v>407670.2218791479</v>
       </c>
       <c r="N68">
-        <v>1.741590909090909</v>
+        <v>1.902494195535734</v>
       </c>
       <c r="O68">
-        <v>1.89075</v>
+        <v>2.084694111942012</v>
       </c>
       <c r="P68">
         <v>50.95877773489349</v>
@@ -4665,7 +4665,7 @@
         <v>106</v>
       </c>
       <c r="I77">
-        <v>10</v>
+        <v>13.76976495726495</v>
       </c>
       <c r="J77">
         <v>8000</v>
@@ -4680,10 +4680,10 @@
         <v>8400184.507055514</v>
       </c>
       <c r="N77">
-        <v>1.741590909090909</v>
+        <v>1.803394296576035</v>
       </c>
       <c r="O77">
-        <v>1.89075</v>
+        <v>1.964819060413116</v>
       </c>
       <c r="P77">
         <v>1050.023063381939</v>
@@ -4824,7 +4824,7 @@
         <v>106</v>
       </c>
       <c r="I80">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="J80">
         <v>8000</v>
@@ -4839,10 +4839,10 @@
         <v>1185598.65949976</v>
       </c>
       <c r="N80">
-        <v>1.741590909090909</v>
+        <v>1.940636870984383</v>
       </c>
       <c r="O80">
-        <v>1.89075</v>
+        <v>2.131200751448103</v>
       </c>
       <c r="P80">
         <v>148.19983243747</v>
@@ -4877,7 +4877,7 @@
         <v>106</v>
       </c>
       <c r="I81">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="J81">
         <v>8000</v>
@@ -4892,10 +4892,10 @@
         <v>374844.5339784805</v>
       </c>
       <c r="N81">
-        <v>1.741590909090909</v>
+        <v>1.803186500133452</v>
       </c>
       <c r="O81">
-        <v>1.89075</v>
+        <v>1.964569140204562</v>
       </c>
       <c r="P81">
         <v>46.85556674731006</v>
@@ -4930,7 +4930,7 @@
         <v>108</v>
       </c>
       <c r="I82">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="J82">
         <v>8000</v>
